--- a/KATALOG_DAMA.xlsx
+++ b/KATALOG_DAMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EE4429-AFCB-4889-B414-7F6451A3CD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7E74E8-3629-456C-8611-12A60B15687A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="15360" windowHeight="8085" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="284">
   <si>
     <t>ALQURAN SAKU RESLETING QURAN MINI TERJEMAHAN | QURAN CANTIK | QURAN SAKU</t>
   </si>
@@ -865,6 +865,18 @@
   </si>
   <si>
     <t>A5 KORAN FAHEEM</t>
+  </si>
+  <si>
+    <t>AL QUR'AN EDISI TAHLILAN 30 Juz + Doa Tahlil | Pengganti Buku Yasin | Al Aqeel A6 Pastel HVS Edisi Tahlilan | BANDUNG</t>
+  </si>
+  <si>
+    <t>Tidak custom</t>
+  </si>
+  <si>
+    <t>Custom sisipan 1 hal</t>
+  </si>
+  <si>
+    <t>Custom sisipan 2 hal</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F8CC9F-DD7D-453D-93E0-632FA723DE62}">
-  <dimension ref="A1:F370"/>
+  <dimension ref="A1:F373"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" style="4" bestFit="1" customWidth="1"/>
@@ -6766,6 +6778,39 @@
         <v>16500</v>
       </c>
     </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D371" t="s">
+        <v>281</v>
+      </c>
+      <c r="F371" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A372" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D372" t="s">
+        <v>282</v>
+      </c>
+      <c r="F372" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D373" t="s">
+        <v>283</v>
+      </c>
+      <c r="F373" s="5">
+        <v>14500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/KATALOG_DAMA.xlsx
+++ b/KATALOG_DAMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7E74E8-3629-456C-8611-12A60B15687A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB16B99A-1500-4BB5-B23D-3D855F6E51CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15360" windowHeight="8085" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="289">
   <si>
     <t>ALQURAN SAKU RESLETING QURAN MINI TERJEMAHAN | QURAN CANTIK | QURAN SAKU</t>
   </si>
@@ -877,6 +877,21 @@
   </si>
   <si>
     <t>Custom sisipan 2 hal</t>
+  </si>
+  <si>
+    <t>Merah,Faheem</t>
+  </si>
+  <si>
+    <t>Biru,Faheem</t>
+  </si>
+  <si>
+    <t>Hijau,Faheem</t>
+  </si>
+  <si>
+    <t>Cokelat,Faheem</t>
+  </si>
+  <si>
+    <t>Random,Faheem</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F8CC9F-DD7D-453D-93E0-632FA723DE62}">
-  <dimension ref="A1:F373"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" style="4" bestFit="1" customWidth="1"/>
@@ -6778,7 +6793,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
         <v>280</v>
       </c>
@@ -6800,7 +6815,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
         <v>280</v>
       </c>
@@ -6809,6 +6824,61 @@
       </c>
       <c r="F373" s="5">
         <v>14500</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B374" t="s">
+        <v>284</v>
+      </c>
+      <c r="F374" s="5">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B375" t="s">
+        <v>285</v>
+      </c>
+      <c r="F375" s="5">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B376" t="s">
+        <v>286</v>
+      </c>
+      <c r="F376" s="5">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A377" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B377" t="s">
+        <v>287</v>
+      </c>
+      <c r="F377" s="5">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B378" t="s">
+        <v>288</v>
+      </c>
+      <c r="F378" s="5">
+        <v>16500</v>
       </c>
     </row>
   </sheetData>

--- a/KATALOG_DAMA.xlsx
+++ b/KATALOG_DAMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB16B99A-1500-4BB5-B23D-3D855F6E51CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD4290-9F6B-48F8-A1B8-582F107467B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
+    <workbookView xWindow="3930" yWindow="2835" windowWidth="15360" windowHeight="8085" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1739,7 +1739,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="3">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1832,7 +1832,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="3">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1925,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="F35" s="3">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2018,7 +2018,7 @@
         <v>16</v>
       </c>
       <c r="F40" s="3">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="3">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -6220,8 +6220,8 @@
       <c r="A321" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="F321" s="5">
-        <v>14500</v>
+      <c r="F321" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -6236,8 +6236,8 @@
       <c r="A323" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="F323" s="5">
-        <v>14500</v>
+      <c r="F323" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="324" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -6274,8 +6274,8 @@
       <c r="A327" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="F327" s="5">
-        <v>14500</v>
+      <c r="F327" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="328" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -6318,8 +6318,8 @@
       <c r="D331" t="s">
         <v>266</v>
       </c>
-      <c r="F331" s="5">
-        <v>14500</v>
+      <c r="F331" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="332" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -6359,8 +6359,8 @@
       <c r="A335" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="F335" s="5">
-        <v>14500</v>
+      <c r="F335" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="336" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -6613,8 +6613,8 @@
       <c r="D354" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F354" s="5">
-        <v>14500</v>
+      <c r="F354" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="355" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -6627,8 +6627,8 @@
       <c r="D355" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F355" s="5">
-        <v>14500</v>
+      <c r="F355" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="356" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -6641,8 +6641,8 @@
       <c r="D356" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F356" s="5">
-        <v>14500</v>
+      <c r="F356" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="357" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -6655,8 +6655,8 @@
       <c r="D357" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F357" s="5">
-        <v>14500</v>
+      <c r="F357" s="3">
+        <v>14900</v>
       </c>
     </row>
     <row r="358" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -6826,7 +6826,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
         <v>271</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
         <v>271</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>271</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>271</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>271</v>
       </c>
